--- a/Matrice des tâches.xlsx
+++ b/Matrice des tâches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matgi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869D7D9A-F686-4B82-BC94-282E84B7DD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28CB982-4614-4E3A-B568-55871326DA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="40">
   <si>
     <t>Matrice de répartition de charges (à remplir à chaque séance)</t>
   </si>
@@ -76,9 +76,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>ex 1.1, 1.2 et 1.3 maths</t>
-  </si>
-  <si>
     <t>ex 2.1 et 2.2 maths</t>
   </si>
   <si>
@@ -88,23 +85,68 @@
     <t>13H45 - 15H45</t>
   </si>
   <si>
-    <t>ex 1.4 maths</t>
-  </si>
-  <si>
     <t>ex 2.3 maths et github et debut du 3</t>
   </si>
   <si>
-    <t>ex 2.4 maths</t>
-  </si>
-  <si>
     <t>3.1.1 et 3.1.2</t>
+  </si>
+  <si>
+    <t>10H30 - 12H30</t>
+  </si>
+  <si>
+    <t>10H30 - 12H32</t>
+  </si>
+  <si>
+    <t>13H45 - 15H48</t>
+  </si>
+  <si>
+    <t>heure a definir</t>
+  </si>
+  <si>
+    <t>ex 1.1.1 a 1.1.6</t>
+  </si>
+  <si>
+    <t>30min</t>
+  </si>
+  <si>
+    <t>ex 1.2.1 a 1.2.4</t>
+  </si>
+  <si>
+    <t>ex 1.3.1 a 1.3.2</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>ex 1.4.1 a 1.4.3</t>
+  </si>
+  <si>
+    <t>ex 2.4.1 a 2.4.3</t>
+  </si>
+  <si>
+    <t>ex 2.5.1 a 2.5.4</t>
+  </si>
+  <si>
+    <t>ex 3.3.1 a 3.3.3</t>
+  </si>
+  <si>
+    <t>ex3.3.4 et 3.3.5</t>
+  </si>
+  <si>
+    <t>ex 2.7.1 a 2.7.3</t>
+  </si>
+  <si>
+    <t>ex 2.6.1 a 2.6.5</t>
+  </si>
+  <si>
+    <t>recherche sur les comportement inter-espece pour but d'implementer des fonctions plus representatives de la faune de la terre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +171,11 @@
     <font>
       <sz val="11"/>
       <color indexed="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -377,11 +424,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="82.26953125" customWidth="1"/>
     <col min="3" max="3" width="13.7265625" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" customWidth="1"/>
     <col min="5" max="8" width="9.1796875" customWidth="1"/>
@@ -393,58 +440,28 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="G7" s="4"/>
     </row>
@@ -502,7 +519,7 @@
         <v>46274</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -524,13 +541,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -539,72 +556,1265 @@
         <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46279</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="5">
+        <v>46279</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C50" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="3" t="s">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="5">
-        <v>46279</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B57" s="5">
+        <v>46283</v>
+      </c>
+      <c r="C57" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="2" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="2"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B59" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="2"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="2"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B78" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B81" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="2"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B87" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B88" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" s="5">
+        <v>46282</v>
+      </c>
+      <c r="C92" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="2"/>
+      <c r="H93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" s="5">
+        <v>46282</v>
+      </c>
+      <c r="C99" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="3"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" s="2"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B101" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>17</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" s="2"/>
+      <c r="B106" s="5"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" s="2"/>
+      <c r="B113" s="5"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" s="2"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" s="2"/>
+      <c r="B120" s="5"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" s="2"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="2"/>
+      <c r="B127" s="5"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="2"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" s="2"/>
+      <c r="B134" s="5"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135" s="2"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="2"/>
+      <c r="B141" s="5"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="2"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="2"/>
+      <c r="B148" s="5"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="2"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" s="2"/>
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" s="2"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A162" s="2"/>
+      <c r="B162" s="5"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A163" s="2"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A169" s="2"/>
+      <c r="B169" s="5"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A170" s="2"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A176" s="2"/>
+      <c r="B176" s="5"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A177" s="2"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A183" s="2"/>
+      <c r="B183" s="5"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A184" s="2"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A190" s="2"/>
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A191" s="2"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A197" s="2"/>
+      <c r="B197" s="5"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A198" s="2"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="3"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A204" s="2"/>
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A205" s="2"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211" s="2"/>
+      <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A212" s="2"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" s="2"/>
+      <c r="B218" s="5"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" s="2"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="3"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" s="2"/>
+      <c r="B225" s="5"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A226" s="2"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
+      <c r="E229" s="3"/>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A232" s="2"/>
+      <c r="B232" s="5"/>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
+      <c r="E236" s="3"/>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A239" s="2"/>
+      <c r="B239" s="5"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" s="2"/>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B242" s="3"/>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B243" s="3"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+      <c r="E243" s="3"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A246" s="2"/>
+      <c r="B246" s="5"/>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A247" s="2"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B249" s="3"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B250" s="3"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
+      <c r="E250" s="3"/>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A253" s="2"/>
+      <c r="B253" s="5"/>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A254" s="2"/>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B256" s="3"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B257" s="3"/>
+      <c r="C257" s="3"/>
+      <c r="D257" s="3"/>
+      <c r="E257" s="3"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A260" s="2"/>
+      <c r="B260" s="5"/>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" s="2"/>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B263" s="3"/>
+      <c r="C263" s="3"/>
+      <c r="D263" s="3"/>
+      <c r="E263" s="3"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B264" s="3"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="3"/>
+      <c r="E264" s="3"/>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A267" s="2"/>
+      <c r="B267" s="5"/>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A268" s="2"/>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B270" s="3"/>
+      <c r="C270" s="3"/>
+      <c r="D270" s="3"/>
+      <c r="E270" s="3"/>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
+      <c r="D271" s="3"/>
+      <c r="E271" s="3"/>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A274" s="2"/>
+      <c r="B274" s="5"/>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A275" s="2"/>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B276" s="2"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B277" s="3"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="3"/>
+      <c r="E277" s="3"/>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B278" s="3"/>
+      <c r="C278" s="3"/>
+      <c r="D278" s="3"/>
+      <c r="E278" s="3"/>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A281" s="2"/>
+      <c r="B281" s="5"/>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A282" s="2"/>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B283" s="2"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
+      <c r="E283" s="2"/>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B284" s="3"/>
+      <c r="C284" s="3"/>
+      <c r="D284" s="3"/>
+      <c r="E284" s="3"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="3"/>
+      <c r="E285" s="3"/>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A288" s="2"/>
+      <c r="B288" s="5"/>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A289" s="2"/>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B290" s="2"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
+      <c r="E290" s="2"/>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B291" s="3"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="3"/>
+      <c r="E291" s="3"/>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A295" s="2"/>
+      <c r="B295" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Matrice des tâches.xlsx
+++ b/Matrice des tâches.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matgi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jujus\Downloads\template_rts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28CB982-4614-4E3A-B568-55871326DA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541B7982-B430-44A8-858A-6EB35A63CFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="47">
   <si>
     <t>Matrice de répartition de charges (à remplir à chaque séance)</t>
   </si>
@@ -88,9 +88,6 @@
     <t>ex 2.3 maths et github et debut du 3</t>
   </si>
   <si>
-    <t>3.1.1 et 3.1.2</t>
-  </si>
-  <si>
     <t>10H30 - 12H30</t>
   </si>
   <si>
@@ -140,6 +137,30 @@
   </si>
   <si>
     <t>recherche sur les comportement inter-espece pour but d'implementer des fonctions plus representatives de la faune de la terre</t>
+  </si>
+  <si>
+    <t>fin du 3.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>3.4 et 3.5</t>
+  </si>
+  <si>
+    <t>fin 3.6</t>
+  </si>
+  <si>
+    <t>3.6.1 et 3.6.2</t>
+  </si>
+  <si>
+    <t>3.1.1</t>
+  </si>
+  <si>
+    <t>3.1.2</t>
+  </si>
+  <si>
+    <t>amélioration des combats (affamés + plus forts et très affamés moins fort)</t>
   </si>
 </sst>
 </file>
@@ -425,93 +446,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H295"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="82.26953125" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" customWidth="1"/>
-    <col min="4" max="4" width="18.7265625" customWidth="1"/>
-    <col min="5" max="8" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" customWidth="1"/>
+    <col min="2" max="2" width="82.265625" customWidth="1"/>
+    <col min="3" max="3" width="13.73046875" customWidth="1"/>
+    <col min="4" max="4" width="18.73046875" customWidth="1"/>
+    <col min="5" max="8" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="2"/>
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -522,10 +543,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B22" s="2" t="s">
         <v>2</v>
       </c>
@@ -539,34 +560,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>18</v>
       </c>
@@ -578,13 +599,13 @@
       </c>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>1</v>
       </c>
@@ -595,10 +616,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -612,34 +633,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>17</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>21</v>
       </c>
@@ -650,7 +671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>1</v>
       </c>
@@ -661,10 +682,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B38" s="2" t="s">
         <v>2</v>
       </c>
@@ -678,9 +699,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -690,12 +711,12 @@
       </c>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>17</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -705,7 +726,7 @@
       </c>
       <c r="E40" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>1</v>
       </c>
@@ -716,10 +737,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B45" s="2" t="s">
         <v>2</v>
       </c>
@@ -733,9 +754,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -745,12 +766,12 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -760,7 +781,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>1</v>
       </c>
@@ -768,13 +789,13 @@
         <v>46280</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="2"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B52" s="2" t="s">
         <v>2</v>
       </c>
@@ -788,9 +809,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
@@ -800,16 +821,22 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>17</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="B54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>1</v>
       </c>
@@ -820,10 +847,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="2"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B59" s="2" t="s">
         <v>2</v>
       </c>
@@ -837,9 +864,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
@@ -849,16 +876,22 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>17</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>1</v>
       </c>
@@ -866,13 +899,13 @@
         <v>46288</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="2"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B66" s="2" t="s">
         <v>2</v>
       </c>
@@ -886,9 +919,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B67" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>15</v>
@@ -898,16 +931,22 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>17</v>
       </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>1</v>
       </c>
@@ -918,10 +957,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="2"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B73" s="2" t="s">
         <v>2</v>
       </c>
@@ -935,9 +974,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -947,16 +986,22 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>17</v>
       </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
+      <c r="B75" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>1</v>
       </c>
@@ -967,10 +1012,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B80" s="2" t="s">
         <v>2</v>
       </c>
@@ -984,9 +1029,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B81" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>15</v>
@@ -996,13 +1041,19 @@
       </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B82" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>1</v>
       </c>
@@ -1010,13 +1061,13 @@
         <v>46290</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" s="2"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B87" s="2" t="s">
         <v>2</v>
       </c>
@@ -1030,9 +1081,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B88" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
@@ -1042,13 +1093,19 @@
       </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B89" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>1</v>
       </c>
@@ -1056,16 +1113,16 @@
         <v>46282</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="2"/>
       <c r="H93" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B94" s="2" t="s">
         <v>2</v>
       </c>
@@ -1079,13 +1136,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -1094,7 +1151,7 @@
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>1</v>
       </c>
@@ -1102,13 +1159,13 @@
         <v>46282</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="2"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B101" s="2" t="s">
         <v>2</v>
       </c>
@@ -1122,16 +1179,16 @@
         <v>5</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -1140,676 +1197,676 @@
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="2"/>
       <c r="B106" s="5"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="2"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="2"/>
       <c r="B113" s="5"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="2"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="2"/>
       <c r="B120" s="5"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="2"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="2"/>
       <c r="B127" s="5"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="2"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="2"/>
       <c r="B134" s="5"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="2"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="2"/>
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="2"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="2"/>
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="2"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="2"/>
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="2"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="2"/>
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" s="2"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" s="2"/>
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="2"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="2"/>
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" s="2"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="2"/>
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="2"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" s="2"/>
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="2"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="2"/>
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="2"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" s="2"/>
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="2"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" s="2"/>
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="2"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" s="2"/>
       <c r="B218" s="5"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" s="2"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" s="2"/>
       <c r="B225" s="5"/>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" s="2"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" s="2"/>
       <c r="B232" s="5"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" s="2"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" s="2"/>
       <c r="B239" s="5"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" s="2"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" s="2"/>
       <c r="B246" s="5"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" s="2"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" s="2"/>
       <c r="B253" s="5"/>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" s="2"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" s="2"/>
       <c r="B260" s="5"/>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261" s="2"/>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A267" s="2"/>
       <c r="B267" s="5"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268" s="2"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274" s="2"/>
       <c r="B274" s="5"/>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275" s="2"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281" s="2"/>
       <c r="B281" s="5"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282" s="2"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288" s="2"/>
       <c r="B288" s="5"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289" s="2"/>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295" s="2"/>
       <c r="B295" s="5"/>
     </row>
